--- a/docs/examples/Invoice_Collection_Ledger.xlsx
+++ b/docs/examples/Invoice_Collection_Ledger.xlsx
@@ -6,11 +6,100 @@
     <sheet name="Payments" sheetId="2" r:id="rId2"/>
     <sheet name="Reversals" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Invoice collection ledger'!$A$1:$AP$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Invoice collection ledger'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Payments'!$A$1:$K$2</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Payments'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Reversals'!$A$1:$A$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Reversals'!$1:$1</definedName>
+  </definedNames>
 </workbook>
+</file>
+
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00;[Red]-#,##0.00"/>
+  </numFmts>
+  <fonts count="1">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+  </fonts>
+  <fills count="1">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+  </fills>
+  <borders count="1">
+    <border/>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1" vertical="top"/>
+    </xf>
+  </cellXfs>
+</styleSheet>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="19" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="15" customWidth="1"/>
+    <col min="11" max="11" width="10" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
+    <col min="13" max="13" width="20" customWidth="1"/>
+    <col min="14" max="14" width="23" customWidth="1"/>
+    <col min="15" max="15" width="19" customWidth="1"/>
+    <col min="16" max="16" width="16" customWidth="1"/>
+    <col min="17" max="17" width="18" customWidth="1"/>
+    <col min="18" max="18" width="22" customWidth="1"/>
+    <col min="19" max="19" width="17" customWidth="1"/>
+    <col min="20" max="20" width="20" customWidth="1"/>
+    <col min="21" max="21" width="28" customWidth="1"/>
+    <col min="22" max="22" width="19" customWidth="1"/>
+    <col min="23" max="23" width="23" customWidth="1"/>
+    <col min="24" max="24" width="16" customWidth="1"/>
+    <col min="25" max="25" width="15" customWidth="1"/>
+    <col min="26" max="26" width="46" customWidth="1"/>
+    <col min="27" max="27" width="18" customWidth="1"/>
+    <col min="28" max="28" width="14" customWidth="1"/>
+    <col min="29" max="29" width="18" customWidth="1"/>
+    <col min="30" max="30" width="20" customWidth="1"/>
+    <col min="31" max="31" width="27" customWidth="1"/>
+    <col min="32" max="32" width="10" customWidth="1" style="2"/>
+    <col min="33" max="33" width="10" customWidth="1" style="2"/>
+    <col min="34" max="34" width="10" customWidth="1" style="2"/>
+    <col min="35" max="35" width="15" customWidth="1" style="2"/>
+    <col min="36" max="36" width="23" customWidth="1" style="2"/>
+    <col min="37" max="37" width="14" customWidth="1" style="2"/>
+    <col min="38" max="38" width="11" customWidth="1" style="2"/>
+    <col min="39" max="39" width="13" customWidth="1" style="2"/>
+    <col min="40" max="40" width="17" customWidth="1" style="2"/>
+    <col min="41" max="41" width="12" customWidth="1" style="2"/>
+    <col min="42" max="42" width="14" customWidth="1" style="2"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -163,6 +252,66 @@
           <t>outstandingDisplay</t>
         </is>
       </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>contributionMarginPercent</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>subtotal</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>tax</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>grossPayments</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>paymentReversalAmount</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>netCollected</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>collected</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>outstanding</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>directCostKnown</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>directCost</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>contribution</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -195,15 +344,11 @@
           <t>BBS Mexico</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
+      <c r="G2" s="1">
+        <v>46244</v>
+      </c>
+      <c r="H2" s="1">
+        <v>46275</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -314,6 +459,42 @@
         <is>
           <t>$32,437.25</t>
         </is>
+      </c>
+      <c r="AE2">
+        <v>40.31</v>
+      </c>
+      <c r="AF2">
+        <v>57437.25</v>
+      </c>
+      <c r="AG2">
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <v>57437.25</v>
+      </c>
+      <c r="AI2">
+        <v>25000</v>
+      </c>
+      <c r="AJ2">
+        <v>0</v>
+      </c>
+      <c r="AK2">
+        <v>25000</v>
+      </c>
+      <c r="AL2">
+        <v>25000</v>
+      </c>
+      <c r="AM2">
+        <v>32437.25</v>
+      </c>
+      <c r="AN2">
+        <v>34280</v>
+      </c>
+      <c r="AO2">
+        <v>34280</v>
+      </c>
+      <c r="AP2">
+        <v>23157.25</v>
       </c>
     </row>
     <row r="3">
@@ -347,15 +528,11 @@
           <t>BBS Mexico</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
+      <c r="G3" s="1">
+        <v>46244</v>
+      </c>
+      <c r="H3" s="1">
+        <v>46275</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -466,14 +643,66 @@
         <is>
           <t>$13,363.31</t>
         </is>
+      </c>
+      <c r="AE3">
+        <v>26.73</v>
+      </c>
+      <c r="AF3">
+        <v>13363.31</v>
+      </c>
+      <c r="AG3">
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <v>13363.31</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>13363.31</v>
+      </c>
+      <c r="AN3">
+        <v>9790.25</v>
+      </c>
+      <c r="AO3">
+        <v>9790.25</v>
+      </c>
+      <c r="AP3">
+        <v>3573.06</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AP3"/>
+  <printOptions horizontalCentered="0" verticalCentered="0"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="19" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="13" customWidth="1"/>
+    <col min="8" max="8" width="13" customWidth="1" style="2"/>
+    <col min="9" max="9" width="10" customWidth="1" style="2"/>
+    <col min="10" max="10" width="11" customWidth="1" style="2"/>
+    <col min="11" max="11" width="10" customWidth="1" style="2"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -483,17 +712,52 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>receivedAt</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>amountMinor</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>reference</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>paymentTimestamp</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>paymentDate</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>grossAmount</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>reversed</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>netAmount</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>amount</t>
         </is>
       </c>
     </row>
@@ -505,28 +769,68 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>2500000</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>WF-WIRE-01</t>
         </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K2">
+        <v>25000</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K2"/>
+  <printOptions horizontalCentered="0" verticalCentered="0"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols/>
   <sheetData>
     <row r="1"/>
   </sheetData>
+  <autoFilter ref="A1:A1"/>
+  <printOptions horizontalCentered="0" verticalCentered="0"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>